--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad\Diplomado\MODULO 2\proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\GitHub\Asistencia_diplomado\backend-control-asistencia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2CBAB8-FDA7-4617-A655-A96E539AFC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243DAEF8-E010-4751-ADF1-92FB2FF51532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6516" yWindow="3432" windowWidth="13620" windowHeight="6924" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2124" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -88,13 +88,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -412,10 +412,10 @@
         <v>46309</v>
       </c>
       <c r="B3" s="3">
-        <v>4.1666666666666664E-2</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="C3" s="3">
-        <v>8.3333333333333329E-2</v>
+        <v>0.58333333333333337</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
